--- a/Tabelas/casos_pandemia.xlsx
+++ b/Tabelas/casos_pandemia.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>597</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
